--- a/Info for group website (Responses).xlsx
+++ b/Info for group website (Responses).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,7 +28,7 @@
     <t>netid?</t>
   </si>
   <si>
-    <t>headshot for display (&lt; 1MB file), so no need a big photo, fun ones is acceptable</t>
+    <t>headshot for display (&lt; 1MB file), so no need a big photo, fun ones is acceptable. If you don't want to display your photo, choose something else appropriate to display on a public website would be good as well.</t>
   </si>
   <si>
     <t>url for your google scholar, make one if you don't have any</t>
@@ -197,6 +197,57 @@
   </si>
   <si>
     <t>Rice University, Biological Sciences with a Biochemistry Concentration and Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Fiona Wong</t>
+  </si>
+  <si>
+    <t>She/her</t>
+  </si>
+  <si>
+    <t>Fw32</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1BoA7tXMIxqQdg3jsfhiuLQeY3Ebk_0Jh</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=OILYlowAAAAJ&amp;view_op=list_works&amp;authuser=2&amp;gmla=APjjwubtYx79NPUPxArLNiQgFgGQxJ2STrIB2V-XwgZhJKdjCZ2wVvO0-qBBOtm95hqBkNF3LHcHSES0EYRbmBO4</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/fiona-wong-604ba93a3/</t>
+  </si>
+  <si>
+    <t>Tag free binder development for sex hormone monitoring</t>
+  </si>
+  <si>
+    <t>Rice University, Biosciences with a Biochemistry Concentration</t>
+  </si>
+  <si>
+    <t>Andrew Man</t>
+  </si>
+  <si>
+    <t>High School Student</t>
+  </si>
+  <si>
+    <t>am585</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1MsRY7yk3xRexzvGYjmNV2PcV_89h4PSB</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=t-sgLMwAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/andrew-man-b13882388?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=ios_app</t>
+  </si>
+  <si>
+    <t>https://github.com/AndrewTMan</t>
+  </si>
+  <si>
+    <t>De novo protein design, RFD3 and AF3 Comparison</t>
+  </si>
+  <si>
+    <t>Obra D. Tompkins High School</t>
   </si>
 </sst>
 </file>
@@ -345,15 +396,19 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O6" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O8" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="15">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Name?" id="2"/>
     <tableColumn name="pronouns (optional) ?" id="3"/>
     <tableColumn name="title (if you're a named fellow, such as K99 fellow, NSF fellow, write in others)" id="4"/>
     <tableColumn name="netid?" id="5"/>
-    <tableColumn name="headshot for display (&lt; 1MB file), so no need a big photo, fun ones is acceptable" id="6"/>
+    <tableColumn name="headshot for display (&lt; 1MB file), so no need a big photo, fun ones is acceptable. If you don't want to display your photo, choose something else appropriate to display on a public website would be good as well." id="6"/>
     <tableColumn name="url for your google scholar, make one if you don't have any" id="7"/>
     <tableColumn name="url for your linkedin, make one if you don't have any. (optional but highly recommended)" id="8"/>
     <tableColumn name="url for your github (optional)" id="9"/>
@@ -800,6 +855,70 @@
         <v>61</v>
       </c>
     </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="6">
+        <v>46043.50072293982</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="6">
+        <v>46043.56386927083</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
@@ -817,10 +936,17 @@
     <hyperlink r:id="rId13" ref="F6"/>
     <hyperlink r:id="rId14" ref="G6"/>
     <hyperlink r:id="rId15" ref="H6"/>
+    <hyperlink r:id="rId16" ref="F7"/>
+    <hyperlink r:id="rId17" ref="G7"/>
+    <hyperlink r:id="rId18" ref="H7"/>
+    <hyperlink r:id="rId19" ref="F8"/>
+    <hyperlink r:id="rId20" ref="G8"/>
+    <hyperlink r:id="rId21" ref="H8"/>
+    <hyperlink r:id="rId22" ref="I8"/>
   </hyperlinks>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId23"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId25"/>
   </tableParts>
 </worksheet>
 </file>